--- a/data/availability/projects/la-vista-developments/el-patio-riva.xlsx
+++ b/data/availability/projects/la-vista-developments/el-patio-riva.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
